--- a/ky/downloads/data-excel/3.a.1.xlsx
+++ b/ky/downloads/data-excel/3.a.1.xlsx
@@ -1,10 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29628"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{275B70FF-AAE6-4541-8F0C-F6BEAF4B44C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -325,7 +326,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
@@ -492,12 +493,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -512,100 +513,75 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
@@ -617,16 +593,13 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="164" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
-    <cellStyle name="Обычный 2" xfId="1"/>
+    <cellStyle name="Обычный 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
@@ -642,9 +615,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Тема Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Стандартная">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -682,9 +655,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Стандартная">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -719,7 +692,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -754,7 +727,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Стандартная">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -927,8 +900,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I38"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:J38"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="37.7109375" customWidth="1"/>
@@ -937,7 +910,7 @@
     <col min="4" max="6" width="9.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>101</v>
       </c>
@@ -952,7 +925,7 @@
       <c r="F1" s="3"/>
       <c r="G1" s="3"/>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
         <v>0</v>
       </c>
@@ -963,924 +936,1013 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="4" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="4" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
         <v>3</v>
       </c>
       <c r="B4" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="C4" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="D4" s="8">
+      <c r="D4" s="7">
         <v>2018</v>
       </c>
-      <c r="E4" s="8">
+      <c r="E4" s="7">
         <v>2019</v>
       </c>
-      <c r="F4" s="8">
+      <c r="F4" s="7">
         <v>2020</v>
       </c>
-      <c r="G4" s="8">
+      <c r="G4" s="7">
         <v>2021</v>
       </c>
-      <c r="H4" s="8">
+      <c r="H4" s="7">
         <v>2022</v>
       </c>
-      <c r="I4" s="8">
+      <c r="I4" s="7">
         <v>2023</v>
       </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5" s="9" t="s">
+      <c r="J4" s="7">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A5" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="10" t="s">
+      <c r="B5" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="C5" s="11" t="s">
+      <c r="C5" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="D5" s="37">
+      <c r="D5" s="31">
         <v>8.3000000000000007</v>
       </c>
-      <c r="E5" s="37">
+      <c r="E5" s="31">
         <v>8.1</v>
       </c>
-      <c r="F5" s="37">
+      <c r="F5" s="31">
         <v>7.6</v>
       </c>
-      <c r="G5" s="40">
+      <c r="G5" s="31">
         <v>6.3</v>
       </c>
-      <c r="H5" s="43">
+      <c r="H5" s="34">
         <v>5.6504815716081698</v>
       </c>
-      <c r="I5" s="43">
+      <c r="I5" s="34">
         <v>5.7627222366917641</v>
       </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A6" s="12" t="s">
+      <c r="J5" s="34">
+        <v>7.2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A6" s="11" t="s">
         <v>76</v>
       </c>
-      <c r="B6" s="13" t="s">
+      <c r="B6" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="C6" s="14" t="s">
+      <c r="C6" s="13" t="s">
         <v>74</v>
       </c>
-      <c r="D6" s="37"/>
-      <c r="E6" s="37"/>
-      <c r="F6" s="37"/>
-      <c r="G6" s="40"/>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A7" s="15" t="s">
+      <c r="D6" s="31"/>
+      <c r="E6" s="31"/>
+      <c r="F6" s="31"/>
+      <c r="G6" s="31"/>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A7" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="B7" s="16" t="s">
+      <c r="B7" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="C7" s="17" t="s">
+      <c r="C7" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="D7" s="38">
+      <c r="D7" s="32">
         <v>17.7</v>
       </c>
-      <c r="E7" s="38">
+      <c r="E7" s="32">
         <v>17.2</v>
       </c>
-      <c r="F7" s="38">
+      <c r="F7" s="32">
         <v>16</v>
       </c>
-      <c r="G7" s="41">
+      <c r="G7" s="32">
         <v>13.4</v>
       </c>
-      <c r="H7" s="44">
+      <c r="H7" s="17">
         <v>11.990552717185041</v>
       </c>
-      <c r="I7" s="44">
+      <c r="I7" s="17">
         <v>12.150374768642443</v>
       </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A8" s="15" t="s">
+      <c r="J7" s="17">
+        <v>15.2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A8" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="16" t="s">
+      <c r="B8" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="C8" s="17" t="s">
+      <c r="C8" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="D8" s="38">
+      <c r="D8" s="32">
         <v>0.5</v>
       </c>
-      <c r="E8" s="38">
+      <c r="E8" s="32">
         <v>0.4</v>
       </c>
-      <c r="F8" s="38">
+      <c r="F8" s="32">
         <v>0.5</v>
       </c>
-      <c r="G8" s="41">
+      <c r="G8" s="32">
         <v>0.4</v>
       </c>
-      <c r="H8" s="44">
+      <c r="H8" s="17">
         <v>0.36686386493060885</v>
       </c>
-      <c r="I8" s="44">
+      <c r="I8" s="17">
         <v>0.33526865592135835</v>
       </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A9" s="19" t="s">
+      <c r="J8" s="17">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A9" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="B9" s="13" t="s">
+      <c r="B9" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="C9" s="20" t="s">
+      <c r="C9" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="D9" s="38"/>
-      <c r="E9" s="38"/>
-      <c r="F9" s="38"/>
-      <c r="G9" s="41"/>
-      <c r="H9" s="44"/>
-      <c r="I9" s="44"/>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A10" s="15" t="s">
+      <c r="D9" s="32"/>
+      <c r="E9" s="32"/>
+      <c r="F9" s="32"/>
+      <c r="G9" s="32"/>
+      <c r="H9" s="17"/>
+      <c r="I9" s="17"/>
+      <c r="J9" s="17"/>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A10" s="14" t="s">
         <v>18</v>
       </c>
-      <c r="B10" s="16" t="s">
+      <c r="B10" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="C10" s="17" t="s">
+      <c r="C10" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="D10" s="38">
+      <c r="D10" s="32">
         <v>6.4</v>
       </c>
-      <c r="E10" s="38">
+      <c r="E10" s="32">
         <v>6.2</v>
       </c>
-      <c r="F10" s="38">
+      <c r="F10" s="32">
         <v>6.2</v>
       </c>
-      <c r="G10" s="41">
+      <c r="G10" s="32">
         <v>5.3</v>
       </c>
-      <c r="H10" s="44">
+      <c r="H10" s="17">
         <v>4.7585078053197183</v>
       </c>
-      <c r="I10" s="44">
+      <c r="I10" s="17">
         <v>4.1862505557986136</v>
       </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A11" s="15" t="s">
+      <c r="J10" s="17">
+        <v>5.7</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A11" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="B11" s="16" t="s">
+      <c r="B11" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="C11" s="17" t="s">
+      <c r="C11" s="16" t="s">
         <v>23</v>
       </c>
-      <c r="D11" s="38">
+      <c r="D11" s="32">
         <v>9.5</v>
       </c>
-      <c r="E11" s="38">
+      <c r="E11" s="32">
         <v>9.1999999999999993</v>
       </c>
-      <c r="F11" s="38">
+      <c r="F11" s="32">
         <v>8.5</v>
       </c>
-      <c r="G11" s="41">
+      <c r="G11" s="32">
         <v>6.9</v>
       </c>
-      <c r="H11" s="44">
+      <c r="H11" s="17">
         <v>6.2147211180387529</v>
       </c>
-      <c r="I11" s="44">
+      <c r="I11" s="17">
         <v>6.7483562655646434</v>
       </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A12" s="22" t="s">
+      <c r="J11" s="17">
+        <v>8.4</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A12" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="B12" s="23" t="s">
+      <c r="B12" s="20" t="s">
         <v>25</v>
       </c>
-      <c r="C12" s="24" t="s">
+      <c r="C12" s="21" t="s">
         <v>26</v>
       </c>
-      <c r="D12" s="38"/>
-      <c r="E12" s="38"/>
-      <c r="F12" s="38"/>
-      <c r="G12" s="41"/>
-      <c r="H12" s="44"/>
-      <c r="I12" s="44"/>
-    </row>
-    <row r="13" spans="1:9" s="27" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="15" t="s">
+      <c r="D12" s="32"/>
+      <c r="E12" s="32"/>
+      <c r="F12" s="32"/>
+      <c r="G12" s="32"/>
+      <c r="H12" s="17"/>
+      <c r="I12" s="17"/>
+      <c r="J12" s="17"/>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A13" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="B13" s="16" t="s">
+      <c r="B13" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="C13" s="17" t="s">
+      <c r="C13" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="D13" s="38">
+      <c r="D13" s="32">
         <v>10.8</v>
       </c>
-      <c r="E13" s="38">
+      <c r="E13" s="32">
         <v>10.9</v>
       </c>
-      <c r="F13" s="38">
+      <c r="F13" s="32">
         <v>9.8000000000000007</v>
       </c>
-      <c r="G13" s="41">
+      <c r="G13" s="32">
         <v>9.1</v>
       </c>
-      <c r="H13" s="44">
+      <c r="H13" s="17">
         <v>6.6299725226642234</v>
       </c>
-      <c r="I13" s="44">
+      <c r="I13" s="17">
         <v>11.721778533441505</v>
       </c>
-    </row>
-    <row r="14" spans="1:9" s="27" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="25" t="s">
+      <c r="J13" s="17">
+        <v>10.4</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A14" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="B14" s="28" t="s">
+      <c r="B14" s="22" t="s">
         <v>31</v>
       </c>
-      <c r="C14" s="26" t="s">
+      <c r="C14" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="D14" s="38">
+      <c r="D14" s="32">
         <v>3.4</v>
       </c>
-      <c r="E14" s="38">
+      <c r="E14" s="32">
         <v>4.4000000000000004</v>
       </c>
-      <c r="F14" s="38">
+      <c r="F14" s="32">
         <v>2.8</v>
       </c>
-      <c r="G14" s="41">
+      <c r="G14" s="32">
         <v>1.9</v>
       </c>
-      <c r="H14" s="44">
+      <c r="H14" s="17">
         <v>1.0045350275012754</v>
       </c>
-      <c r="I14" s="44">
+      <c r="I14" s="17">
         <v>0.39226026012037718</v>
       </c>
-    </row>
-    <row r="15" spans="1:9" s="27" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="25" t="s">
+      <c r="J14" s="17">
+        <v>5.3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A15" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="B15" s="16" t="s">
+      <c r="B15" s="15" t="s">
         <v>34</v>
       </c>
-      <c r="C15" s="26" t="s">
+      <c r="C15" s="16" t="s">
         <v>35</v>
       </c>
-      <c r="D15" s="38">
+      <c r="D15" s="32">
         <v>17.899999999999999</v>
       </c>
-      <c r="E15" s="38">
+      <c r="E15" s="32">
         <v>17</v>
       </c>
-      <c r="F15" s="38">
+      <c r="F15" s="32">
         <v>15.7</v>
       </c>
-      <c r="G15" s="41">
+      <c r="G15" s="32">
         <v>15.2</v>
       </c>
-      <c r="H15" s="44">
+      <c r="H15" s="17">
         <v>15.32109744080277</v>
       </c>
-      <c r="I15" s="44">
+      <c r="I15" s="17">
         <v>15.431347214780089</v>
       </c>
-    </row>
-    <row r="16" spans="1:9" s="27" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="25" t="s">
+      <c r="J15" s="17">
+        <v>14.6</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A16" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="B16" s="16" t="s">
+      <c r="B16" s="15" t="s">
         <v>37</v>
       </c>
-      <c r="C16" s="26" t="s">
+      <c r="C16" s="16" t="s">
         <v>38</v>
       </c>
-      <c r="D16" s="38">
+      <c r="D16" s="32">
         <v>14.7</v>
       </c>
-      <c r="E16" s="38">
+      <c r="E16" s="32">
         <v>13.8</v>
       </c>
-      <c r="F16" s="38">
+      <c r="F16" s="32">
         <v>14.2</v>
       </c>
-      <c r="G16" s="41">
+      <c r="G16" s="32">
         <v>12.7</v>
       </c>
-      <c r="H16" s="44">
+      <c r="H16" s="17">
         <v>11.932654937916501</v>
       </c>
-      <c r="I16" s="44">
+      <c r="I16" s="17">
         <v>12.56881331951053</v>
       </c>
-    </row>
-    <row r="17" spans="1:9" s="27" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="25" t="s">
+      <c r="J16" s="17">
+        <v>12.4</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A17" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="B17" s="16" t="s">
+      <c r="B17" s="15" t="s">
         <v>40</v>
       </c>
-      <c r="C17" s="26" t="s">
+      <c r="C17" s="16" t="s">
         <v>41</v>
       </c>
-      <c r="D17" s="38">
+      <c r="D17" s="32">
         <v>6.7</v>
       </c>
-      <c r="E17" s="38">
+      <c r="E17" s="32">
         <v>6</v>
       </c>
-      <c r="F17" s="38">
+      <c r="F17" s="32">
         <v>6.2</v>
       </c>
-      <c r="G17" s="41">
+      <c r="G17" s="32">
         <v>4.3</v>
       </c>
-      <c r="H17" s="44">
+      <c r="H17" s="17">
         <v>4.4024960942722968</v>
       </c>
-      <c r="I17" s="44">
+      <c r="I17" s="17">
         <v>4.9361801817513591</v>
       </c>
-    </row>
-    <row r="18" spans="1:9" s="27" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="25" t="s">
+      <c r="J17" s="17">
+        <v>5.6</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A18" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="B18" s="16" t="s">
+      <c r="B18" s="15" t="s">
         <v>43</v>
       </c>
-      <c r="C18" s="26" t="s">
+      <c r="C18" s="16" t="s">
         <v>44</v>
       </c>
-      <c r="D18" s="38">
+      <c r="D18" s="32">
         <v>13</v>
       </c>
-      <c r="E18" s="38">
+      <c r="E18" s="32">
         <v>13.7</v>
       </c>
-      <c r="F18" s="38">
+      <c r="F18" s="32">
         <v>13.5</v>
       </c>
-      <c r="G18" s="41">
+      <c r="G18" s="32">
         <v>13</v>
       </c>
-      <c r="H18" s="44">
+      <c r="H18" s="17">
         <v>13.275841712798133</v>
       </c>
-      <c r="I18" s="44">
+      <c r="I18" s="17">
         <v>13.92788271827051</v>
       </c>
-    </row>
-    <row r="19" spans="1:9" s="27" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="25" t="s">
+      <c r="J18" s="17">
+        <v>12.4</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A19" s="14" t="s">
         <v>45</v>
       </c>
-      <c r="B19" s="21" t="s">
+      <c r="B19" s="18" t="s">
         <v>46</v>
       </c>
-      <c r="C19" s="26" t="s">
+      <c r="C19" s="16" t="s">
         <v>47</v>
       </c>
-      <c r="D19" s="38">
+      <c r="D19" s="32">
         <v>12.2</v>
       </c>
-      <c r="E19" s="38">
+      <c r="E19" s="32">
         <v>10.5</v>
       </c>
-      <c r="F19" s="38">
+      <c r="F19" s="32">
         <v>9.4</v>
       </c>
-      <c r="G19" s="41">
+      <c r="G19" s="32">
         <v>7.8</v>
       </c>
-      <c r="H19" s="44">
+      <c r="H19" s="17">
         <v>5.5953228746387378</v>
       </c>
-      <c r="I19" s="44">
+      <c r="I19" s="17">
         <v>5.796504268446359</v>
       </c>
-    </row>
-    <row r="20" spans="1:9" s="27" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="15" t="s">
+      <c r="J19" s="17">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A20" s="14" t="s">
         <v>48</v>
       </c>
-      <c r="B20" s="21" t="s">
+      <c r="B20" s="18" t="s">
         <v>49</v>
       </c>
-      <c r="C20" s="17" t="s">
+      <c r="C20" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="D20" s="38">
+      <c r="D20" s="32">
         <v>6.2</v>
       </c>
-      <c r="E20" s="38">
+      <c r="E20" s="32">
         <v>6.3</v>
       </c>
-      <c r="F20" s="38">
+      <c r="F20" s="32">
         <v>7.3</v>
       </c>
-      <c r="G20" s="41">
+      <c r="G20" s="32">
         <v>5.5</v>
       </c>
-      <c r="H20" s="44">
+      <c r="H20" s="17">
         <v>5.7561942305949083</v>
       </c>
-      <c r="I20" s="44">
+      <c r="I20" s="17">
         <v>3.6469692666385813</v>
       </c>
-    </row>
-    <row r="21" spans="1:9" s="27" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="25" t="s">
+      <c r="J20" s="17">
+        <v>5.6</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A21" s="14" t="s">
         <v>51</v>
       </c>
-      <c r="B21" s="16" t="s">
+      <c r="B21" s="15" t="s">
         <v>52</v>
       </c>
-      <c r="C21" s="26" t="s">
+      <c r="C21" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="D21" s="38">
+      <c r="D21" s="32">
         <v>1.8</v>
       </c>
-      <c r="E21" s="38">
+      <c r="E21" s="32">
         <v>1.6</v>
       </c>
-      <c r="F21" s="38">
+      <c r="F21" s="32">
         <v>1.3</v>
       </c>
-      <c r="G21" s="41">
+      <c r="G21" s="32">
         <v>1.2</v>
       </c>
-      <c r="H21" s="44">
+      <c r="H21" s="17">
         <v>0.91260128840317045</v>
       </c>
-      <c r="I21" s="44">
+      <c r="I21" s="17">
         <v>1.2344990530700553</v>
       </c>
-    </row>
-    <row r="22" spans="1:9" s="27" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="19" t="s">
+      <c r="J21" s="17">
+        <v>1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A22" s="11" t="s">
         <v>78</v>
       </c>
-      <c r="B22" s="13" t="s">
+      <c r="B22" s="12" t="s">
         <v>77</v>
       </c>
-      <c r="C22" s="20" t="s">
+      <c r="C22" s="13" t="s">
         <v>79</v>
       </c>
-      <c r="D22" s="38"/>
-      <c r="E22" s="38"/>
-      <c r="F22" s="38"/>
-      <c r="G22" s="41"/>
-      <c r="H22" s="44"/>
-      <c r="I22" s="44"/>
-    </row>
-    <row r="23" spans="1:9" s="27" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="25" t="s">
+      <c r="D22" s="32"/>
+      <c r="E22" s="32"/>
+      <c r="F22" s="32"/>
+      <c r="G22" s="32"/>
+      <c r="H22" s="17"/>
+      <c r="I22" s="17"/>
+      <c r="J22" s="17"/>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A23" s="14" t="s">
         <v>80</v>
       </c>
-      <c r="B23" s="16" t="s">
+      <c r="B23" s="15" t="s">
         <v>80</v>
       </c>
-      <c r="C23" s="26" t="s">
+      <c r="C23" s="16" t="s">
         <v>80</v>
       </c>
-      <c r="D23" s="38">
+      <c r="D23" s="32">
         <v>0.4</v>
       </c>
-      <c r="E23" s="38">
+      <c r="E23" s="32">
         <v>0.3</v>
       </c>
-      <c r="F23" s="38">
+      <c r="F23" s="32">
         <v>0.4</v>
       </c>
-      <c r="G23" s="41">
+      <c r="G23" s="32">
         <v>0.1</v>
       </c>
-      <c r="H23" s="44">
+      <c r="H23" s="17">
         <v>0.12558892880771302</v>
       </c>
-      <c r="I23" s="44">
+      <c r="I23" s="17">
         <v>0.33854574252686492</v>
       </c>
-    </row>
-    <row r="24" spans="1:9" s="27" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="25" t="s">
+      <c r="J23" s="17">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A24" s="14" t="s">
         <v>81</v>
       </c>
-      <c r="B24" s="16" t="s">
+      <c r="B24" s="15" t="s">
         <v>81</v>
       </c>
-      <c r="C24" s="26" t="s">
+      <c r="C24" s="16" t="s">
         <v>81</v>
       </c>
-      <c r="D24" s="38">
+      <c r="D24" s="32">
         <v>10.6</v>
       </c>
-      <c r="E24" s="38">
+      <c r="E24" s="32">
         <v>10</v>
       </c>
-      <c r="F24" s="38">
+      <c r="F24" s="32">
         <v>9.4</v>
       </c>
-      <c r="G24" s="41">
+      <c r="G24" s="32">
         <v>7.4</v>
       </c>
-      <c r="H24" s="44">
+      <c r="H24" s="17">
         <v>6.813728136595028</v>
       </c>
-      <c r="I24" s="44">
+      <c r="I24" s="17">
         <v>7.0095823182535142</v>
       </c>
-    </row>
-    <row r="25" spans="1:9" s="27" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="25" t="s">
+      <c r="J24" s="17">
+        <v>8.5</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A25" s="14" t="s">
         <v>82</v>
       </c>
-      <c r="B25" s="16" t="s">
+      <c r="B25" s="15" t="s">
         <v>82</v>
       </c>
-      <c r="C25" s="26" t="s">
+      <c r="C25" s="16" t="s">
         <v>82</v>
       </c>
-      <c r="D25" s="38">
+      <c r="D25" s="32">
         <v>10</v>
       </c>
-      <c r="E25" s="38">
+      <c r="E25" s="32">
         <v>10.199999999999999</v>
       </c>
-      <c r="F25" s="38">
+      <c r="F25" s="32">
         <v>9.4</v>
       </c>
-      <c r="G25" s="41">
+      <c r="G25" s="32">
         <v>9</v>
       </c>
-      <c r="H25" s="44">
+      <c r="H25" s="17">
         <v>7.4835121062312364</v>
       </c>
-      <c r="I25" s="44">
+      <c r="I25" s="17">
         <v>7.4180588363268161</v>
       </c>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A26" s="22" t="s">
+      <c r="J25" s="17">
+        <v>9.6999999999999993</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A26" s="19" t="s">
         <v>84</v>
       </c>
-      <c r="B26" s="29" t="s">
+      <c r="B26" s="23" t="s">
         <v>83</v>
       </c>
-      <c r="C26" s="30" t="s">
+      <c r="C26" s="24" t="s">
         <v>85</v>
       </c>
-      <c r="D26" s="38"/>
-      <c r="E26" s="38"/>
-      <c r="F26" s="38"/>
-      <c r="G26" s="41"/>
-      <c r="H26" s="44"/>
-      <c r="I26" s="44"/>
-    </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A27" s="31" t="s">
+      <c r="D26" s="32"/>
+      <c r="E26" s="32"/>
+      <c r="F26" s="32"/>
+      <c r="G26" s="32"/>
+      <c r="H26" s="17"/>
+      <c r="I26" s="17"/>
+      <c r="J26" s="17"/>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A27" s="25" t="s">
         <v>87</v>
       </c>
-      <c r="B27" s="32" t="s">
+      <c r="B27" s="26" t="s">
         <v>86</v>
       </c>
-      <c r="C27" s="16" t="s">
+      <c r="C27" s="15" t="s">
         <v>98</v>
       </c>
-      <c r="D27" s="38">
+      <c r="D27" s="32">
         <v>2.8</v>
       </c>
-      <c r="E27" s="38">
+      <c r="E27" s="32">
         <v>3.4</v>
       </c>
-      <c r="F27" s="38">
+      <c r="F27" s="32">
         <v>2.8</v>
       </c>
-      <c r="G27" s="41">
+      <c r="G27" s="32">
         <v>1.5</v>
       </c>
-      <c r="H27" s="44">
+      <c r="H27" s="17">
         <v>1.0698262411858328</v>
       </c>
-      <c r="I27" s="44">
+      <c r="I27" s="17">
         <v>1.3575537444685963</v>
       </c>
-    </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A28" s="31" t="s">
+      <c r="J27" s="17">
+        <v>1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A28" s="25" t="s">
         <v>54</v>
       </c>
-      <c r="B28" s="32" t="s">
+      <c r="B28" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="C28" s="16" t="s">
+      <c r="C28" s="15" t="s">
         <v>88</v>
       </c>
-      <c r="D28" s="38">
+      <c r="D28" s="32">
         <v>3.5</v>
       </c>
-      <c r="E28" s="38">
+      <c r="E28" s="32">
         <v>2.9</v>
       </c>
-      <c r="F28" s="38">
+      <c r="F28" s="32">
         <v>3.8</v>
       </c>
-      <c r="G28" s="41">
+      <c r="G28" s="32">
         <v>2.9</v>
       </c>
-      <c r="H28" s="44">
+      <c r="H28" s="17">
         <v>2.525977374670846</v>
       </c>
-      <c r="I28" s="44">
+      <c r="I28" s="17">
         <v>3.7000582818073822</v>
       </c>
-    </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A29" s="31" t="s">
+      <c r="J28" s="17">
+        <v>3.2</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A29" s="25" t="s">
         <v>56</v>
       </c>
-      <c r="B29" s="32" t="s">
+      <c r="B29" s="26" t="s">
         <v>57</v>
       </c>
-      <c r="C29" s="16" t="s">
+      <c r="C29" s="15" t="s">
         <v>89</v>
       </c>
-      <c r="D29" s="38">
+      <c r="D29" s="32">
         <v>9.8000000000000007</v>
       </c>
-      <c r="E29" s="38">
+      <c r="E29" s="32">
         <v>9.3000000000000007</v>
       </c>
-      <c r="F29" s="38">
+      <c r="F29" s="32">
         <v>8.8000000000000007</v>
       </c>
-      <c r="G29" s="41">
+      <c r="G29" s="32">
         <v>7.4</v>
       </c>
-      <c r="H29" s="44">
+      <c r="H29" s="17">
         <v>6.9014261042903025</v>
       </c>
-      <c r="I29" s="44">
+      <c r="I29" s="17">
         <v>7.0145832826742662</v>
       </c>
-    </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A30" s="31" t="s">
+      <c r="J29" s="17">
+        <v>9.1999999999999993</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A30" s="25" t="s">
         <v>58</v>
       </c>
-      <c r="B30" s="32" t="s">
+      <c r="B30" s="26" t="s">
         <v>59</v>
       </c>
-      <c r="C30" s="16" t="s">
+      <c r="C30" s="15" t="s">
         <v>90</v>
       </c>
-      <c r="D30" s="38">
+      <c r="D30" s="32">
         <v>11.7</v>
       </c>
-      <c r="E30" s="38">
+      <c r="E30" s="32">
         <v>11.8</v>
       </c>
-      <c r="F30" s="38">
+      <c r="F30" s="32">
         <v>10.8</v>
       </c>
-      <c r="G30" s="41">
+      <c r="G30" s="32">
         <v>9.1</v>
       </c>
-      <c r="H30" s="44">
+      <c r="H30" s="17">
         <v>7.9091356334900151</v>
       </c>
-      <c r="I30" s="44">
+      <c r="I30" s="17">
         <v>7.601388319014589</v>
       </c>
-    </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A31" s="31" t="s">
+      <c r="J30" s="17">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A31" s="25" t="s">
         <v>60</v>
       </c>
-      <c r="B31" s="32" t="s">
+      <c r="B31" s="26" t="s">
         <v>61</v>
       </c>
-      <c r="C31" s="16" t="s">
+      <c r="C31" s="15" t="s">
         <v>91</v>
       </c>
-      <c r="D31" s="38">
+      <c r="D31" s="32">
         <v>5.6</v>
       </c>
-      <c r="E31" s="38">
+      <c r="E31" s="32">
         <v>5.5</v>
       </c>
-      <c r="F31" s="38">
+      <c r="F31" s="32">
         <v>4.9000000000000004</v>
       </c>
-      <c r="G31" s="41">
+      <c r="G31" s="32">
         <v>4.0999999999999996</v>
       </c>
-      <c r="H31" s="44">
+      <c r="H31" s="17">
         <v>3.3800067710254136</v>
       </c>
-      <c r="I31" s="44">
+      <c r="I31" s="17">
         <v>3.2001807961995414</v>
       </c>
-    </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A32" s="30" t="s">
+      <c r="J31" s="17">
+        <v>4.8</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A32" s="24" t="s">
         <v>62</v>
       </c>
-      <c r="B32" s="29" t="s">
+      <c r="B32" s="23" t="s">
         <v>63</v>
       </c>
-      <c r="C32" s="30" t="s">
+      <c r="C32" s="24" t="s">
         <v>92</v>
       </c>
-      <c r="D32" s="38"/>
-      <c r="E32" s="38"/>
-      <c r="F32" s="38"/>
-      <c r="G32" s="41"/>
-      <c r="H32" s="44"/>
-      <c r="I32" s="44"/>
-    </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A33" s="33" t="s">
+      <c r="D32" s="32"/>
+      <c r="E32" s="32"/>
+      <c r="F32" s="32"/>
+      <c r="G32" s="32"/>
+      <c r="H32" s="17"/>
+      <c r="I32" s="17"/>
+      <c r="J32" s="17"/>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A33" s="27" t="s">
         <v>64</v>
       </c>
-      <c r="B33" s="32" t="s">
+      <c r="B33" s="26" t="s">
         <v>65</v>
       </c>
-      <c r="C33" s="16" t="s">
+      <c r="C33" s="15" t="s">
         <v>93</v>
       </c>
-      <c r="D33" s="38">
+      <c r="D33" s="32">
         <v>8</v>
       </c>
-      <c r="E33" s="38">
+      <c r="E33" s="32">
         <v>8.1999999999999993</v>
       </c>
-      <c r="F33" s="38">
+      <c r="F33" s="32">
         <v>7.9</v>
       </c>
-      <c r="G33" s="41">
+      <c r="G33" s="32">
         <v>6.4</v>
       </c>
-      <c r="H33" s="44">
+      <c r="H33" s="17">
         <v>4.7357406632935053</v>
       </c>
-      <c r="I33" s="44">
+      <c r="I33" s="17">
         <v>6.1374688939827911</v>
       </c>
-    </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A34" s="33" t="s">
+      <c r="J33" s="17">
+        <v>6.8</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A34" s="27" t="s">
         <v>66</v>
       </c>
-      <c r="B34" s="32" t="s">
+      <c r="B34" s="26" t="s">
         <v>67</v>
       </c>
-      <c r="C34" s="16" t="s">
+      <c r="C34" s="15" t="s">
         <v>94</v>
       </c>
-      <c r="D34" s="38">
+      <c r="D34" s="32">
         <v>7.4</v>
       </c>
-      <c r="E34" s="38">
+      <c r="E34" s="32">
         <v>7.8</v>
       </c>
-      <c r="F34" s="38">
+      <c r="F34" s="32">
         <v>6.9</v>
       </c>
-      <c r="G34" s="41">
+      <c r="G34" s="32">
         <v>6.2</v>
       </c>
-      <c r="H34" s="44">
+      <c r="H34" s="17">
         <v>4.7664658340238164</v>
       </c>
-      <c r="I34" s="44">
+      <c r="I34" s="17">
         <v>5.522716841454633</v>
       </c>
-    </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A35" s="33" t="s">
+      <c r="J34" s="17">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A35" s="27" t="s">
         <v>68</v>
       </c>
-      <c r="B35" s="32" t="s">
+      <c r="B35" s="26" t="s">
         <v>69</v>
       </c>
-      <c r="C35" s="16" t="s">
+      <c r="C35" s="15" t="s">
         <v>95</v>
       </c>
-      <c r="D35" s="38">
+      <c r="D35" s="32">
         <v>8.5</v>
       </c>
-      <c r="E35" s="38">
+      <c r="E35" s="32">
         <v>7.7</v>
       </c>
-      <c r="F35" s="38">
+      <c r="F35" s="32">
         <v>8</v>
       </c>
-      <c r="G35" s="41">
+      <c r="G35" s="32">
         <v>5.4</v>
       </c>
-      <c r="H35" s="44">
+      <c r="H35" s="17">
         <v>5.4209310439574798</v>
       </c>
-      <c r="I35" s="44">
+      <c r="I35" s="17">
         <v>5.959494359842247</v>
       </c>
-    </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A36" s="33" t="s">
+      <c r="J35" s="17">
+        <v>6.4</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A36" s="27" t="s">
         <v>70</v>
       </c>
-      <c r="B36" s="32" t="s">
+      <c r="B36" s="26" t="s">
         <v>71</v>
       </c>
-      <c r="C36" s="16" t="s">
+      <c r="C36" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="D36" s="38">
+      <c r="D36" s="32">
         <v>8.5</v>
       </c>
-      <c r="E36" s="38">
+      <c r="E36" s="32">
         <v>8</v>
       </c>
-      <c r="F36" s="38">
+      <c r="F36" s="32">
         <v>7.2</v>
       </c>
-      <c r="G36" s="41">
+      <c r="G36" s="32">
         <v>6.6</v>
       </c>
-      <c r="H36" s="44">
+      <c r="H36" s="17">
         <v>6.4917222807546029</v>
       </c>
-      <c r="I36" s="44">
+      <c r="I36" s="17">
         <v>5.4831892692336535</v>
       </c>
-    </row>
-    <row r="37" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="34" t="s">
+      <c r="J36" s="17">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="28" t="s">
         <v>72</v>
       </c>
-      <c r="B37" s="35" t="s">
+      <c r="B37" s="29" t="s">
         <v>73</v>
       </c>
-      <c r="C37" s="36" t="s">
+      <c r="C37" s="30" t="s">
         <v>97</v>
       </c>
-      <c r="D37" s="39">
+      <c r="D37" s="33">
         <v>9.6</v>
       </c>
-      <c r="E37" s="39">
+      <c r="E37" s="33">
         <v>8.8000000000000007</v>
       </c>
-      <c r="F37" s="39">
+      <c r="F37" s="33">
         <v>8.1</v>
       </c>
-      <c r="G37" s="42">
+      <c r="G37" s="33">
         <v>7.2</v>
       </c>
-      <c r="H37" s="45">
+      <c r="H37" s="35">
         <v>6.4231110817165149</v>
       </c>
-      <c r="I37" s="45">
+      <c r="I37" s="35">
         <v>5.7612749525079918</v>
       </c>
-    </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="D38" s="18"/>
-      <c r="E38" s="18"/>
-      <c r="F38" s="18"/>
-      <c r="G38" s="18"/>
+      <c r="J37" s="35">
+        <v>7.7</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="D38" s="17"/>
+      <c r="E38" s="17"/>
+      <c r="F38" s="17"/>
+      <c r="G38" s="17"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
